--- a/Team-Data/2014-15/1-17-2014-15.xlsx
+++ b/Team-Data/2014-15/1-17-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.805</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I2" t="n">
         <v>37.9</v>
       </c>
       <c r="J2" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.471</v>
@@ -691,13 +758,13 @@
         <v>24.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.389</v>
+        <v>0.388</v>
       </c>
       <c r="O2" t="n">
         <v>17.8</v>
       </c>
       <c r="P2" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0.772</v>
@@ -712,16 +779,16 @@
         <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W2" t="n">
         <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
         <v>4.8</v>
@@ -733,13 +800,13 @@
         <v>21.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC2" t="n">
         <v>6.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -763,28 +830,28 @@
         <v>4</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
         <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
         <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>25</v>
@@ -793,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -811,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -951,7 +1018,7 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>17</v>
@@ -969,22 +1036,22 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
       </c>
       <c r="AX3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY3" t="n">
         <v>24</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>25</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -993,7 +1060,7 @@
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
         <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>0.415</v>
+        <v>0.425</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1046,46 +1113,46 @@
         <v>81.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N4" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R4" t="n">
         <v>9.6</v>
       </c>
       <c r="S4" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T4" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="n">
         <v>4.6</v>
@@ -1094,16 +1161,16 @@
         <v>20.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
@@ -1115,7 +1182,7 @@
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1124,7 +1191,7 @@
         <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1133,7 +1200,7 @@
         <v>17</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>22</v>
@@ -1142,28 +1209,28 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1172,13 +1239,13 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="H5" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I5" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J5" t="n">
-        <v>85</v>
+        <v>84.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.426</v>
+        <v>0.429</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.309</v>
+        <v>0.313</v>
       </c>
       <c r="O5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.738</v>
+        <v>0.741</v>
       </c>
       <c r="R5" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S5" t="n">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
       <c r="T5" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V5" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W5" t="n">
         <v>5.7</v>
@@ -1270,25 +1337,25 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA5" t="n">
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
@@ -1297,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>24</v>
@@ -1306,7 +1373,7 @@
         <v>11</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>27</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR5" t="n">
         <v>23</v>
@@ -1333,10 +1400,10 @@
         <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,16 +1415,16 @@
         <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
         <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.643</v>
+        <v>0.659</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1410,37 +1477,37 @@
         <v>82.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N6" t="n">
         <v>0.363</v>
       </c>
       <c r="O6" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="P6" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T6" t="n">
         <v>45.4</v>
       </c>
       <c r="U6" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
         <v>14.3</v>
@@ -1449,34 +1516,34 @@
         <v>6.3</v>
       </c>
       <c r="X6" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
         <v>18.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>7</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>13</v>
@@ -1488,7 +1555,7 @@
         <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1506,22 +1573,22 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1530,10 +1597,10 @@
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
@@ -1661,7 +1728,7 @@
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
@@ -1685,13 +1752,13 @@
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS7" t="n">
         <v>27</v>
@@ -1703,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>22</v>
@@ -1724,7 +1791,7 @@
         <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
         <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
@@ -1771,7 +1838,7 @@
         <v>40.9</v>
       </c>
       <c r="J8" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
@@ -1780,34 +1847,34 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
         <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1816,34 +1883,34 @@
         <v>4.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" t="n">
         <v>20.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>108.7</v>
+        <v>108.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,22 +1928,22 @@
         <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT8" t="n">
         <v>17</v>
@@ -1891,7 +1958,7 @@
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -1935,34 +2002,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
         <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.45</v>
+        <v>0.462</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J9" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="N9" t="n">
         <v>0.321</v>
@@ -1974,25 +2041,25 @@
         <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.739</v>
+        <v>0.736</v>
       </c>
       <c r="R9" t="n">
         <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="T9" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="U9" t="n">
         <v>21.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
         <v>4.8</v>
@@ -2004,19 +2071,19 @@
         <v>23.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
@@ -2025,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2034,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>13</v>
@@ -2052,22 +2119,22 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
         <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2085,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -2117,64 +2184,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J10" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="O10" t="n">
         <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.699</v>
+        <v>0.696</v>
       </c>
       <c r="R10" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T10" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
         <v>13.4</v>
       </c>
       <c r="W10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="X10" t="n">
         <v>4.6</v>
@@ -2183,22 +2250,22 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2207,10 +2274,10 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ10" t="n">
         <v>6</v>
@@ -2225,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
@@ -2252,16 +2319,16 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA10" t="n">
         <v>23</v>
@@ -2270,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -2299,46 +2366,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.842</v>
+        <v>0.838</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="J11" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.485</v>
+        <v>0.483</v>
       </c>
       <c r="L11" t="n">
         <v>10.1</v>
       </c>
       <c r="M11" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="N11" t="n">
         <v>0.385</v>
       </c>
       <c r="O11" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.775</v>
+        <v>0.78</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -2347,10 +2414,10 @@
         <v>34.5</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.1</v>
@@ -2359,7 +2426,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" t="n">
         <v>3.6</v>
@@ -2368,16 +2435,16 @@
         <v>19.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>110</v>
+        <v>109.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2395,13 +2462,13 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
@@ -2410,13 +2477,13 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>24</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
         <v>4</v>
@@ -2446,7 +2513,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -2484,58 +2551,58 @@
         <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.675</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J12" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.714</v>
+        <v>0.711</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S12" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>21</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
         <v>9.800000000000001</v>
@@ -2544,43 +2611,43 @@
         <v>4.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>12</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
         <v>19</v>
@@ -2619,22 +2686,22 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
         <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -2663,67 +2730,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.357</v>
+        <v>0.366</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J13" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="L13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
         <v>20.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.332</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P13" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S13" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="T13" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W13" t="n">
         <v>5.9</v>
       </c>
       <c r="X13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y13" t="n">
         <v>5.1</v>
@@ -2732,76 +2799,76 @@
         <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
         <v>23</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ13" t="n">
         <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
         <v>18</v>
@@ -2810,13 +2877,13 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.659</v>
+        <v>0.65</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.472</v>
@@ -2875,34 +2942,34 @@
         <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P14" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="R14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T14" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="W14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X14" t="n">
         <v>4.6</v>
@@ -2914,25 +2981,25 @@
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.9</v>
+        <v>106.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
         <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2959,28 +3026,28 @@
         <v>5</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT14" t="n">
         <v>26</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
         <v>3</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0.293</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M15" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>12.7</v>
@@ -3087,25 +3154,25 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,19 +3184,19 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL15" t="n">
         <v>23</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>20</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
@@ -3138,16 +3205,16 @@
         <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
         <v>21</v>
@@ -3156,25 +3223,25 @@
         <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0.725</v>
+        <v>0.718</v>
       </c>
       <c r="H16" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I16" t="n">
         <v>39</v>
       </c>
       <c r="J16" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
         <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P16" t="n">
         <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
         <v>22.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
@@ -3275,10 +3342,10 @@
         <v>5.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB16" t="n">
         <v>101.9</v>
@@ -3287,13 +3354,13 @@
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>4</v>
@@ -3305,10 +3372,10 @@
         <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3317,22 +3384,22 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
         <v>16</v>
@@ -3362,7 +3429,7 @@
         <v>13</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -3469,16 +3536,16 @@
         <v>-3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH17" t="n">
         <v>29</v>
@@ -3499,16 +3566,16 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>25</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3666,13 +3733,13 @@
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL18" t="n">
         <v>22</v>
@@ -3687,13 +3754,13 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
         <v>23</v>
@@ -3720,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -3755,106 +3822,106 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.179</v>
+        <v>0.158</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J19" t="n">
-        <v>85.5</v>
+        <v>85.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>5.2</v>
       </c>
       <c r="M19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.341</v>
       </c>
       <c r="O19" t="n">
         <v>18.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="R19" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S19" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="T19" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U19" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V19" t="n">
         <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA19" t="n">
         <v>21.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG19" t="n">
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3869,10 +3936,10 @@
         <v>7</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3890,7 +3957,7 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -3937,103 +4004,103 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.474</v>
+        <v>0.487</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.7</v>
+        <v>84.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
@@ -4042,7 +4109,7 @@
         <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN20" t="n">
         <v>20</v>
@@ -4051,46 +4118,46 @@
         <v>14</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-9.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4227,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>28</v>
@@ -4251,10 +4318,10 @@
         <v>17</v>
       </c>
       <c r="AV21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4391,7 +4458,7 @@
         <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4418,13 +4485,13 @@
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
@@ -4439,16 +4506,16 @@
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ22" t="n">
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.357</v>
+        <v>0.349</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
         <v>0.368</v>
@@ -4522,55 +4589,55 @@
         <v>19.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
         <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG23" t="n">
         <v>25</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>23</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -4579,7 +4646,7 @@
         <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
@@ -4588,7 +4655,7 @@
         <v>18</v>
       </c>
       <c r="AM23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4615,7 +4682,7 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
         <v>17</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -4665,61 +4732,61 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J24" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.412</v>
+        <v>0.411</v>
       </c>
       <c r="L24" t="n">
         <v>7.1</v>
       </c>
       <c r="M24" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.297</v>
+        <v>0.298</v>
       </c>
       <c r="O24" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="P24" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.678</v>
+        <v>0.676</v>
       </c>
       <c r="R24" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T24" t="n">
         <v>41.9</v>
       </c>
       <c r="U24" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V24" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="W24" t="n">
         <v>10</v>
@@ -4731,19 +4798,19 @@
         <v>5.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB24" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.2</v>
+        <v>-12</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4776,16 +4843,16 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,16 +4870,16 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -4946,10 +5013,10 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4958,7 +5025,7 @@
         <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
         <v>23</v>
@@ -4970,13 +5037,13 @@
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
         <v>26</v>
@@ -4985,7 +5052,7 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.732</v>
+        <v>0.75</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J26" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L26" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O26" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P26" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>35</v>
+        <v>35.3</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W26" t="n">
         <v>6.6</v>
@@ -5101,13 +5168,13 @@
         <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5119,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
@@ -5131,13 +5198,13 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5149,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5161,7 +5228,7 @@
         <v>9</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H27" t="n">
         <v>48.8</v>
       </c>
       <c r="I27" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="K27" t="n">
         <v>0.458</v>
@@ -5238,37 +5305,37 @@
         <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O27" t="n">
         <v>23.2</v>
       </c>
       <c r="P27" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="S27" t="n">
         <v>33.7</v>
       </c>
       <c r="T27" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="U27" t="n">
         <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
@@ -5277,19 +5344,19 @@
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
         <v>20</v>
@@ -5301,7 +5368,7 @@
         <v>20</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5328,10 +5395,10 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
         <v>6</v>
@@ -5340,7 +5407,7 @@
         <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -5393,67 +5460,67 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H28" t="n">
         <v>49.1</v>
       </c>
       <c r="I28" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="O28" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="U28" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V28" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5465,13 +5532,13 @@
         <v>20.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC28" t="n">
         <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5483,25 +5550,25 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>20</v>
@@ -5510,7 +5577,7 @@
         <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,34 +5586,34 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>10</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>12</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>5.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="n">
         <v>6</v>
@@ -5692,7 +5759,7 @@
         <v>6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
         <v>11</v>
@@ -5704,19 +5771,19 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
         <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-3</v>
       </c>
       <c r="AD30" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5844,7 +5911,7 @@
         <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5865,19 +5932,19 @@
         <v>18</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>13</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>24</v>
@@ -5895,7 +5962,7 @@
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5910,7 +5977,7 @@
         <v>23</v>
       </c>
       <c r="BC30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F31" t="n">
         <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L31" t="n">
         <v>6</v>
@@ -5969,25 +6036,25 @@
         <v>15.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.386</v>
+        <v>0.388</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.745</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U31" t="n">
         <v>24.9</v>
@@ -5999,40 +6066,40 @@
         <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA31" t="n">
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF31" t="n">
         <v>6</v>
       </c>
       <c r="AG31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
         <v>20</v>
@@ -6047,22 +6114,22 @@
         <v>29</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6071,22 +6138,22 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
         <v>9</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-17-2014-15</t>
+          <t>2015-01-17</t>
         </is>
       </c>
     </row>
